--- a/material-externo/salida/revision_material_externo.xlsx
+++ b/material-externo/salida/revision_material_externo.xlsx
@@ -11,15 +11,16 @@
     <sheet sheetId="5" name="grafía parecida" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="significados (Hoppe 1974)" state="visible" r:id="rId9"/>
     <sheet sheetId="7" name="reglas" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="ya resueltas" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="texto por traducir (opcional)" state="visible" r:id="rId12"/>
+    <sheet sheetId="8" name="u por ʉ en el corpus" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="ya resueltas" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="texto por traducir (opcional)" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4301" uniqueCount="1426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4435" uniqueCount="1505">
   <si>
     <t>REVISIÓN DEL MATERIAL EXTERNO — para el revisor (21 de octubre de 2026)</t>
   </si>
@@ -3114,6 +3115,255 @@
     <t>La luna… / La casa…</t>
   </si>
   <si>
+    <t>como está escrita en las oraciones</t>
+  </si>
+  <si>
+    <t>forma con ʉ del vocabulario</t>
+  </si>
+  <si>
+    <t>veces</t>
+  </si>
+  <si>
+    <t>ejemplo</t>
+  </si>
+  <si>
+    <t>¿Es la misma palabra? (sí: se corrige a ʉ / no: son dos palabras)</t>
+  </si>
+  <si>
+    <t>duma</t>
+  </si>
+  <si>
+    <t>dʉma</t>
+  </si>
+  <si>
+    <t>Fuerza</t>
+  </si>
+  <si>
+    <t>Indzui zhʉnguashkʉ, Josénzhe anzhinguiandzina burrunandzina duma tshijtuʉn nukuantka Siquem kushamke.</t>
+  </si>
+  <si>
+    <t>naiun</t>
+  </si>
+  <si>
+    <t>naiʉn</t>
+  </si>
+  <si>
+    <t>no  se va</t>
+  </si>
+  <si>
+    <t>Ukuashkangua ingui faraónga kakaia israelitandzina naiún mʉnantkua. Jehovága Moisés angasha awantka ingui faraón tuʉn na</t>
+  </si>
+  <si>
+    <t>nanunkurra</t>
+  </si>
+  <si>
+    <t>nanʉnkurra</t>
+  </si>
+  <si>
+    <t>debemos</t>
+  </si>
+  <si>
+    <t>Dzinguaka: “Umba makuma aunkurra go ukuzhi bʉgui urraga ingui shkua torre go aunkurra katshijkiamaka ijtuna. Memé nekunk</t>
+  </si>
+  <si>
+    <t>nekunkurra</t>
+  </si>
+  <si>
+    <t>nekʉnkurra</t>
+  </si>
+  <si>
+    <t>trato</t>
+  </si>
+  <si>
+    <t>Ijkʉnaga dzinguaka: “Nawi nekunkurra kʉ Jehovága naishizha aunuka”.</t>
+  </si>
+  <si>
+    <t>guagun</t>
+  </si>
+  <si>
+    <t>Isaac ingui Rebecaga ijkakandunún nanantka Esaúga Jacob guaga awega, memé nunkuame kʉzhia: “Naia ushi kaiarru makuma ush</t>
+  </si>
+  <si>
+    <t>bugui</t>
+  </si>
+  <si>
+    <t>bʉgui</t>
+  </si>
+  <si>
+    <t>miles</t>
+  </si>
+  <si>
+    <t>Abraham bugüi we ugunga nanantka</t>
+  </si>
+  <si>
+    <t>nujkunanun</t>
+  </si>
+  <si>
+    <t>nʉjkʉnanun</t>
+  </si>
+  <si>
+    <t>No tengo</t>
+  </si>
+  <si>
+    <t>nujkunanún</t>
+  </si>
+  <si>
+    <t>ashaiun</t>
+  </si>
+  <si>
+    <t>ashaiʉn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soldadundzinarru kaia: “Kuisa ashaiún mʉnantkua ñi dzui zi zhisozún mʉnantkua”. “Ima terrua naka awantka ashe awega bou </t>
+  </si>
+  <si>
+    <t>kunaka</t>
+  </si>
+  <si>
+    <t>kʉnaka</t>
+  </si>
+  <si>
+    <t>le dio miedo</t>
+  </si>
+  <si>
+    <t>Mema azhi neka ukuaga bʉgui kʉjka kunaka awantka David, ingui nanzhe kawandzinangua kʉjka kakʉnzhanantka.</t>
+  </si>
+  <si>
+    <t>dzinaiun</t>
+  </si>
+  <si>
+    <t>dzinaiʉn</t>
+  </si>
+  <si>
+    <t>iban</t>
+  </si>
+  <si>
+    <t>Ukuemdzi Jehovága kaia awantka dzui atungʉrna washi zhanandzina dzinaiún nanunguashi Herodes nugeku.</t>
+  </si>
+  <si>
+    <t>kungui</t>
+  </si>
+  <si>
+    <t>kʉngui</t>
+  </si>
+  <si>
+    <t>todas</t>
+  </si>
+  <si>
+    <t>nabiga we uguana aunkurrerru uguanunkurra Kunkujshinaga nabitijka ikuia zukuega kungüi aúnka</t>
+  </si>
+  <si>
+    <t>kun</t>
+  </si>
+  <si>
+    <t>kʉn</t>
+  </si>
+  <si>
+    <t>madero</t>
+  </si>
+  <si>
+    <t>Ukuashkʉ kangʉma Gosénzherga, israelitandzina tshijkuaga nunkueku, ñi shkuangua tábano kun nananka.</t>
+  </si>
+  <si>
+    <t>ingugun</t>
+  </si>
+  <si>
+    <t>ingʉgun</t>
+  </si>
+  <si>
+    <t>Quitar</t>
+  </si>
+  <si>
+    <t>Ingui, anzhʉngʉma wida ukuashkʉ, Atalíaga ʉnkʉmasha awantka zhaguashe awega Judáka. nenegangua zhaguashaiama ingugún nan</t>
+  </si>
+  <si>
+    <t>ku</t>
+  </si>
+  <si>
+    <t>kʉ</t>
+  </si>
+  <si>
+    <t>todo</t>
+  </si>
+  <si>
+    <t>¡Ku dusha dzawantka 12 canastandzinamba!</t>
+  </si>
+  <si>
+    <t>aguñi</t>
+  </si>
+  <si>
+    <t>agʉñi</t>
+  </si>
+  <si>
+    <t>demás</t>
+  </si>
+  <si>
+    <t>ima Kunkujshinanzhe zhinzhomamba nuka nainguneka aguñi we uguanega</t>
+  </si>
+  <si>
+    <t>ijkuna</t>
+  </si>
+  <si>
+    <t>ijkʉna</t>
+  </si>
+  <si>
+    <t>Ellos</t>
+  </si>
+  <si>
+    <t>ijkuna azhi yazhigunga</t>
+  </si>
+  <si>
+    <t>nunka</t>
+  </si>
+  <si>
+    <t>nʉnka</t>
+  </si>
+  <si>
+    <t>será</t>
+  </si>
+  <si>
+    <t>nabi shinya kuaga inzhina Jehowa nunka ingüi inzhina Jesús nunka</t>
+  </si>
+  <si>
+    <t>mula</t>
+  </si>
+  <si>
+    <t>mʉla</t>
+  </si>
+  <si>
+    <t>dimorar</t>
+  </si>
+  <si>
+    <t>nabiga Kunkujshinanzhe zhinzhoma nujkúa aunkurrerru mula kuankurra</t>
+  </si>
+  <si>
+    <t>nujkunananka</t>
+  </si>
+  <si>
+    <t>nʉjkʉnananka</t>
+  </si>
+  <si>
+    <t>tuve</t>
+  </si>
+  <si>
+    <t>kunananka</t>
+  </si>
+  <si>
+    <t>kʉnananka</t>
+  </si>
+  <si>
+    <t>tuvo</t>
+  </si>
+  <si>
+    <t>kununka</t>
+  </si>
+  <si>
+    <t>kʉnʉnka</t>
+  </si>
+  <si>
+    <t>Tiene</t>
+  </si>
+  <si>
     <t>palabra damana</t>
   </si>
   <si>
@@ -3162,12 +3412,6 @@
     <t>saltar</t>
   </si>
   <si>
-    <t>kʉn</t>
-  </si>
-  <si>
-    <t>madero</t>
-  </si>
-  <si>
     <t>madera</t>
   </si>
   <si>
@@ -3256,12 +3500,6 @@
   </si>
   <si>
     <t>neboa (masa de yuca)</t>
-  </si>
-  <si>
-    <t>nʉnka</t>
-  </si>
-  <si>
-    <t>será</t>
   </si>
   <si>
     <t>será; va a</t>
@@ -4827,6 +5065,3093 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H118"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="4" width="24" customWidth="1"/>
+    <col min="5" max="6" width="60" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>1206</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>1207</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>1208</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>1212</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>1215</v>
+      </c>
+      <c r="G4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>1218</v>
+      </c>
+      <c r="G5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>1220</v>
+      </c>
+      <c r="G6" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>1223</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>1228</v>
+      </c>
+      <c r="G9" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>1231</v>
+      </c>
+      <c r="G10" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>1233</v>
+      </c>
+      <c r="G11" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>1236</v>
+      </c>
+      <c r="G12" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>1240</v>
+      </c>
+      <c r="G14" t="s">
+        <v>1</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>1243</v>
+      </c>
+      <c r="G15" t="s">
+        <v>1</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>1246</v>
+      </c>
+      <c r="G16" t="s">
+        <v>1</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>1248</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G17" t="s">
+        <v>1</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>1251</v>
+      </c>
+      <c r="G18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>1254</v>
+      </c>
+      <c r="G19" t="s">
+        <v>1</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>1256</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G20" t="s">
+        <v>1</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>1259</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G22" t="s">
+        <v>1</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>1264</v>
+      </c>
+      <c r="G23" t="s">
+        <v>1</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>1266</v>
+      </c>
+      <c r="G24" t="s">
+        <v>1</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>1269</v>
+      </c>
+      <c r="G25" t="s">
+        <v>1</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>1271</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>1274</v>
+      </c>
+      <c r="G27" t="s">
+        <v>1</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="G28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="G29" t="s">
+        <v>1</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>1281</v>
+      </c>
+      <c r="G30" t="s">
+        <v>1</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="G31" t="s">
+        <v>1</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>1286</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G32" t="s">
+        <v>1</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>1289</v>
+      </c>
+      <c r="G33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="G34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>1294</v>
+      </c>
+      <c r="G35" t="s">
+        <v>1</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="G36" t="s">
+        <v>1</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>1299</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G37" t="s">
+        <v>1</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>1302</v>
+      </c>
+      <c r="G38" t="s">
+        <v>1</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>1305</v>
+      </c>
+      <c r="G39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>1308</v>
+      </c>
+      <c r="G40" t="s">
+        <v>1</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>1313</v>
+      </c>
+      <c r="G42" t="s">
+        <v>1</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>1316</v>
+      </c>
+      <c r="G43" t="s">
+        <v>1</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>1318</v>
+      </c>
+      <c r="G44" t="s">
+        <v>1</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>1320</v>
+      </c>
+      <c r="G45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>1323</v>
+      </c>
+      <c r="G46" t="s">
+        <v>1</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>1212</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G47" t="s">
+        <v>1</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>1327</v>
+      </c>
+      <c r="G48" t="s">
+        <v>1</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>1333</v>
+      </c>
+      <c r="G50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>1335</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G51" t="s">
+        <v>1</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>1338</v>
+      </c>
+      <c r="G52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>1341</v>
+      </c>
+      <c r="G53" t="s">
+        <v>1</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>1344</v>
+      </c>
+      <c r="G54" t="s">
+        <v>1</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>1346</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G55" t="s">
+        <v>1</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>1349</v>
+      </c>
+      <c r="G56" t="s">
+        <v>1</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>1352</v>
+      </c>
+      <c r="G57" t="s">
+        <v>1</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>1354</v>
+      </c>
+      <c r="G58" t="s">
+        <v>1</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>1357</v>
+      </c>
+      <c r="G59" t="s">
+        <v>1</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>1359</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G60" t="s">
+        <v>1</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>1362</v>
+      </c>
+      <c r="G61" t="s">
+        <v>1</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B62" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>1365</v>
+      </c>
+      <c r="G62" t="s">
+        <v>1</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B63" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>1367</v>
+      </c>
+      <c r="G63" t="s">
+        <v>1</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B64" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G64" t="s">
+        <v>1</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>1372</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G65" t="s">
+        <v>1</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>1375</v>
+      </c>
+      <c r="G66" t="s">
+        <v>1</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B67" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>1378</v>
+      </c>
+      <c r="G67" t="s">
+        <v>1</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B68" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>1380</v>
+      </c>
+      <c r="G68" t="s">
+        <v>1</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B69" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G69" t="s">
+        <v>1</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B70" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>1385</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G70" t="s">
+        <v>1</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B71" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>1388</v>
+      </c>
+      <c r="G71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B72" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>1391</v>
+      </c>
+      <c r="G72" t="s">
+        <v>1</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B73" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="G73" t="s">
+        <v>1</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B74" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>1396</v>
+      </c>
+      <c r="G74" t="s">
+        <v>1</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B75" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>1398</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G75" t="s">
+        <v>1</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B76" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="G76" t="s">
+        <v>1</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="G77" t="s">
+        <v>1</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B78" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>1406</v>
+      </c>
+      <c r="G78" t="s">
+        <v>1</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B79" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>1408</v>
+      </c>
+      <c r="G79" t="s">
+        <v>1</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B80" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>1411</v>
+      </c>
+      <c r="G80" t="s">
+        <v>1</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B81" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G81" t="s">
+        <v>1</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B82" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>1416</v>
+      </c>
+      <c r="G82" t="s">
+        <v>1</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B83" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>1419</v>
+      </c>
+      <c r="G83" t="s">
+        <v>1</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>1421</v>
+      </c>
+      <c r="B84" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>1422</v>
+      </c>
+      <c r="G84" t="s">
+        <v>1</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B85" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>1424</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G85" t="s">
+        <v>1</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B86" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>1427</v>
+      </c>
+      <c r="G86" t="s">
+        <v>1</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B87" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E87" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>1430</v>
+      </c>
+      <c r="G87" t="s">
+        <v>1</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B88" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>1433</v>
+      </c>
+      <c r="G88" t="s">
+        <v>1</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B89" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>1435</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G89" t="s">
+        <v>1</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B90" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>1438</v>
+      </c>
+      <c r="G90" t="s">
+        <v>1</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B91" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E91" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>1441</v>
+      </c>
+      <c r="G91" t="s">
+        <v>1</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B92" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E92" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>1443</v>
+      </c>
+      <c r="G92" t="s">
+        <v>1</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B93" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>1446</v>
+      </c>
+      <c r="G93" t="s">
+        <v>1</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B94" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E94" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>1449</v>
+      </c>
+      <c r="G94" t="s">
+        <v>1</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B95" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E95" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>1452</v>
+      </c>
+      <c r="G95" t="s">
+        <v>1</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>1454</v>
+      </c>
+      <c r="B96" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E96" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>1455</v>
+      </c>
+      <c r="G96" t="s">
+        <v>1</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>1457</v>
+      </c>
+      <c r="B97" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>1458</v>
+      </c>
+      <c r="G97" t="s">
+        <v>1</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B98" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>1460</v>
+      </c>
+      <c r="G98" t="s">
+        <v>1</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B99" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E99" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>1462</v>
+      </c>
+      <c r="G99" t="s">
+        <v>1</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B100" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E100" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G100" t="s">
+        <v>1</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>1465</v>
+      </c>
+      <c r="B101" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E101" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>1466</v>
+      </c>
+      <c r="G101" t="s">
+        <v>1</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>1467</v>
+      </c>
+      <c r="B102" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E102" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>1468</v>
+      </c>
+      <c r="G102" t="s">
+        <v>1</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>1469</v>
+      </c>
+      <c r="B103" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E103" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>1470</v>
+      </c>
+      <c r="G103" t="s">
+        <v>1</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>1471</v>
+      </c>
+      <c r="B104" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E104" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>1472</v>
+      </c>
+      <c r="G104" t="s">
+        <v>1</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B105" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E105" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>1475</v>
+      </c>
+      <c r="G105" t="s">
+        <v>1</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>1477</v>
+      </c>
+      <c r="B106" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E106" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>1478</v>
+      </c>
+      <c r="G106" t="s">
+        <v>1</v>
+      </c>
+      <c r="H106" s="3" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B107" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E107" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>1480</v>
+      </c>
+      <c r="G107" t="s">
+        <v>1</v>
+      </c>
+      <c r="H107" s="3" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B108" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E108" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>1482</v>
+      </c>
+      <c r="G108" t="s">
+        <v>1</v>
+      </c>
+      <c r="H108" s="3" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>1483</v>
+      </c>
+      <c r="B109" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E109" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>1484</v>
+      </c>
+      <c r="G109" t="s">
+        <v>1</v>
+      </c>
+      <c r="H109" s="3" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>1485</v>
+      </c>
+      <c r="B110" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E110" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>1486</v>
+      </c>
+      <c r="G110" t="s">
+        <v>1</v>
+      </c>
+      <c r="H110" s="3" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B111" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E111" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>1488</v>
+      </c>
+      <c r="G111" t="s">
+        <v>1</v>
+      </c>
+      <c r="H111" s="3" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>1489</v>
+      </c>
+      <c r="B112" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E112" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>1490</v>
+      </c>
+      <c r="G112" t="s">
+        <v>1</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>1492</v>
+      </c>
+      <c r="B113" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E113" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>1493</v>
+      </c>
+      <c r="G113" t="s">
+        <v>1</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B114" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E114" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="G114" t="s">
+        <v>1</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>1497</v>
+      </c>
+      <c r="B115" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E115" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>1498</v>
+      </c>
+      <c r="G115" t="s">
+        <v>1</v>
+      </c>
+      <c r="H115" s="3" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>1499</v>
+      </c>
+      <c r="B116" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E116" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>1500</v>
+      </c>
+      <c r="G116" t="s">
+        <v>1</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B117" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E117" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>1502</v>
+      </c>
+      <c r="G117" t="s">
+        <v>1</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B118" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E118" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>1504</v>
+      </c>
+      <c r="G118" t="s">
+        <v>1</v>
+      </c>
+      <c r="H118" s="3" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H201"/>
@@ -16677,6 +20002,606 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="7" customWidth="1"/>
+    <col min="6" max="6" width="60" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E2">
+        <v>8</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>1039</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>1043</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>1047</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>1051</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>1053</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E8">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>1061</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>1064</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>1071</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>1072</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>1076</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>1088</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>1091</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>1096</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>1104</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>1105</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>1110</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>1108</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" sqref="G10:G22">
+      <formula1>"sí, la misma,no, son dos palabras,no sé"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G2:G22">
+      <formula1>"sí, la misma,no, son dos palabras,no sé"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -16692,19 +20617,19 @@
         <v>19</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1031</v>
+        <v>1114</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1032</v>
+        <v>1115</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1033</v>
+        <v>1116</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1034</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -16712,13 +20637,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>1035</v>
+        <v>1118</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1036</v>
+        <v>1119</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>1037</v>
+        <v>1120</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>29</v>
@@ -16735,10 +20660,10 @@
         <v>567</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1038</v>
+        <v>1121</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1039</v>
+        <v>1122</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>29</v>
@@ -16752,10 +20677,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1040</v>
+        <v>1123</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1041</v>
+        <v>1124</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>125</v>
@@ -16772,13 +20697,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1042</v>
+        <v>1125</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1043</v>
+        <v>1126</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>1044</v>
+        <v>1127</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>29</v>
@@ -16795,10 +20720,10 @@
         <v>752</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1045</v>
+        <v>1128</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>1046</v>
+        <v>1129</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>29</v>
@@ -16812,13 +20737,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1047</v>
+        <v>1078</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1048</v>
+        <v>1079</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>1049</v>
+        <v>1130</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>29</v>
@@ -16832,13 +20757,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1050</v>
+        <v>1131</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1051</v>
+        <v>1132</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>1052</v>
+        <v>1133</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>29</v>
@@ -16852,13 +20777,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1053</v>
+        <v>1134</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1054</v>
+        <v>1135</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>1055</v>
+        <v>1136</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>29</v>
@@ -16872,13 +20797,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>1056</v>
+        <v>1137</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1057</v>
+        <v>1138</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>1058</v>
+        <v>1139</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>29</v>
@@ -16892,13 +20817,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1059</v>
+        <v>1140</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1060</v>
+        <v>1141</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>1061</v>
+        <v>1142</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>29</v>
@@ -16912,10 +20837,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>1062</v>
+        <v>1143</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1063</v>
+        <v>1144</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>781</v>
@@ -16932,13 +20857,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>1064</v>
+        <v>1145</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1065</v>
+        <v>1146</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>1066</v>
+        <v>1147</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>220</v>
@@ -16952,10 +20877,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>1067</v>
+        <v>1148</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1068</v>
+        <v>1149</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>665</v>
@@ -16972,13 +20897,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>1069</v>
+        <v>1150</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1070</v>
+        <v>1151</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>1071</v>
+        <v>1152</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>220</v>
@@ -16992,13 +20917,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>1072</v>
+        <v>1153</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>1073</v>
+        <v>1154</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>1074</v>
+        <v>1155</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>220</v>
@@ -17012,13 +20937,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>1072</v>
+        <v>1153</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>1073</v>
+        <v>1154</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>1075</v>
+        <v>1156</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>220</v>
@@ -17032,13 +20957,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>1076</v>
+        <v>1157</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>1077</v>
+        <v>1158</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>1078</v>
+        <v>1159</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>220</v>
@@ -17052,13 +20977,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>1079</v>
+        <v>1098</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>1080</v>
+        <v>1099</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>1081</v>
+        <v>1160</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>220</v>
@@ -17072,13 +20997,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>1082</v>
+        <v>1161</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1083</v>
+        <v>1162</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>1084</v>
+        <v>1163</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>220</v>
@@ -17092,13 +21017,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>1062</v>
+        <v>1143</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>1063</v>
+        <v>1144</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>1085</v>
+        <v>1164</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>220</v>
@@ -17112,13 +21037,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>1086</v>
+        <v>1165</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>1087</v>
+        <v>1166</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>1088</v>
+        <v>1167</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>232</v>
@@ -17132,13 +21057,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>1089</v>
+        <v>1168</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>1090</v>
+        <v>1169</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>1091</v>
+        <v>1170</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>35</v>
@@ -17152,13 +21077,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>1053</v>
+        <v>1134</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>1054</v>
+        <v>1135</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>1055</v>
+        <v>1136</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>35</v>
@@ -17172,13 +21097,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>1092</v>
+        <v>1171</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>1093</v>
+        <v>1172</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>1094</v>
+        <v>1173</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>35</v>
@@ -17192,13 +21117,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>1095</v>
+        <v>1174</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>1096</v>
+        <v>1175</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>1097</v>
+        <v>1176</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>35</v>
@@ -17212,13 +21137,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>1035</v>
+        <v>1118</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>1036</v>
+        <v>1119</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>1037</v>
+        <v>1120</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>35</v>
@@ -17232,10 +21157,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>1098</v>
+        <v>1177</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>1099</v>
+        <v>1178</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>113</v>
@@ -17252,13 +21177,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>1100</v>
+        <v>1179</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>1101</v>
+        <v>1180</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>1102</v>
+        <v>1181</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>35</v>
@@ -17272,13 +21197,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>1103</v>
+        <v>1182</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>1104</v>
+        <v>1183</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>1105</v>
+        <v>1184</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>35</v>
@@ -17292,13 +21217,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>1106</v>
+        <v>1185</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>1107</v>
+        <v>1186</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>1108</v>
+        <v>1187</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>35</v>
@@ -17312,13 +21237,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>1109</v>
+        <v>1188</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>1110</v>
+        <v>1189</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>1111</v>
+        <v>1190</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>35</v>
@@ -17332,13 +21257,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>1112</v>
+        <v>1191</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>1113</v>
+        <v>1192</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>1114</v>
+        <v>1193</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>35</v>
@@ -17352,10 +21277,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>1115</v>
+        <v>1194</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>1116</v>
+        <v>1195</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>710</v>
@@ -17372,3106 +21297,19 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>1059</v>
+        <v>1140</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>1060</v>
+        <v>1141</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>1117</v>
+        <v>1196</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H118"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="4" width="24" customWidth="1"/>
-    <col min="5" max="6" width="60" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="40" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>1118</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1119</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1120</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>1121</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>1122</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>1123</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>1124</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>1125</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>1126</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>1127</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>1128</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>1129</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>1130</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1131</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>1133</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>1134</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>1135</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>1136</v>
-      </c>
-      <c r="G4" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>1137</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>1138</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>1139</v>
-      </c>
-      <c r="G5" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>1137</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>1140</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>1141</v>
-      </c>
-      <c r="G6" t="s">
-        <v>1</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>1142</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>1143</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>1144</v>
-      </c>
-      <c r="G7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>1142</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>1145</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>1146</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G8" t="s">
-        <v>1</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>1147</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>1148</v>
-      </c>
-      <c r="B9" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>1149</v>
-      </c>
-      <c r="G9" t="s">
-        <v>1</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>1151</v>
-      </c>
-      <c r="B10" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>1152</v>
-      </c>
-      <c r="G10" t="s">
-        <v>1</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>1153</v>
-      </c>
-      <c r="B11" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>1154</v>
-      </c>
-      <c r="G11" t="s">
-        <v>1</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>1155</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>1156</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>1157</v>
-      </c>
-      <c r="G12" t="s">
-        <v>1</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>1155</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>1158</v>
-      </c>
-      <c r="B13" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>1095</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G13" t="s">
-        <v>1</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>1159</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>1160</v>
-      </c>
-      <c r="B14" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>1161</v>
-      </c>
-      <c r="G14" t="s">
-        <v>1</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>1162</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>1163</v>
-      </c>
-      <c r="B15" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>1164</v>
-      </c>
-      <c r="G15" t="s">
-        <v>1</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>1165</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>1166</v>
-      </c>
-      <c r="B16" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>1167</v>
-      </c>
-      <c r="G16" t="s">
-        <v>1</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>1165</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>1168</v>
-      </c>
-      <c r="B17" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>1169</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G17" t="s">
-        <v>1</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>1170</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>1171</v>
-      </c>
-      <c r="B18" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>1172</v>
-      </c>
-      <c r="G18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>1173</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>1174</v>
-      </c>
-      <c r="B19" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>1175</v>
-      </c>
-      <c r="G19" t="s">
-        <v>1</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>1173</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>1176</v>
-      </c>
-      <c r="B20" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>1177</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G20" t="s">
-        <v>1</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>1178</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>1179</v>
-      </c>
-      <c r="B21" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>1180</v>
-      </c>
-      <c r="G21" t="s">
-        <v>1</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B22" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>1183</v>
-      </c>
-      <c r="G22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>1184</v>
-      </c>
-      <c r="B23" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>1185</v>
-      </c>
-      <c r="G23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>1186</v>
-      </c>
-      <c r="B24" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>1187</v>
-      </c>
-      <c r="G24" t="s">
-        <v>1</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>1188</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>1189</v>
-      </c>
-      <c r="B25" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>1190</v>
-      </c>
-      <c r="G25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>1188</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>1191</v>
-      </c>
-      <c r="B26" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>1192</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G26" t="s">
-        <v>1</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>1193</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>1194</v>
-      </c>
-      <c r="B27" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>1195</v>
-      </c>
-      <c r="G27" t="s">
-        <v>1</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>1196</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>1197</v>
-      </c>
-      <c r="B28" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>1198</v>
-      </c>
-      <c r="G28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>1196</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>1199</v>
-      </c>
-      <c r="B29" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>1200</v>
-      </c>
-      <c r="G29" t="s">
-        <v>1</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>1196</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>1201</v>
-      </c>
-      <c r="B30" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>1202</v>
-      </c>
-      <c r="G30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>1203</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>1204</v>
-      </c>
-      <c r="B31" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>1205</v>
-      </c>
-      <c r="G31" t="s">
-        <v>1</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>1203</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>1206</v>
-      </c>
-      <c r="B32" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>1207</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>1208</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>1209</v>
-      </c>
-      <c r="B33" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>1210</v>
-      </c>
-      <c r="G33" t="s">
-        <v>1</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>1212</v>
-      </c>
-      <c r="B34" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>1213</v>
-      </c>
-      <c r="G34" t="s">
-        <v>1</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>1214</v>
-      </c>
-      <c r="B35" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>1215</v>
-      </c>
-      <c r="G35" t="s">
-        <v>1</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>1216</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B36" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>1218</v>
-      </c>
-      <c r="G36" t="s">
-        <v>1</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>1216</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B37" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>1220</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G37" t="s">
-        <v>1</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>1221</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>1222</v>
-      </c>
-      <c r="B38" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>1223</v>
-      </c>
-      <c r="G38" t="s">
-        <v>1</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>1224</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>1225</v>
-      </c>
-      <c r="B39" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>1226</v>
-      </c>
-      <c r="G39" t="s">
-        <v>1</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>1227</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>1228</v>
-      </c>
-      <c r="B40" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>1229</v>
-      </c>
-      <c r="G40" t="s">
-        <v>1</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>1227</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>1230</v>
-      </c>
-      <c r="B41" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>1231</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>1232</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>1233</v>
-      </c>
-      <c r="B42" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>1234</v>
-      </c>
-      <c r="G42" t="s">
-        <v>1</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>1235</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>1236</v>
-      </c>
-      <c r="B43" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>1237</v>
-      </c>
-      <c r="G43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>1235</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>1238</v>
-      </c>
-      <c r="B44" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>1239</v>
-      </c>
-      <c r="G44" t="s">
-        <v>1</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>1235</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>1240</v>
-      </c>
-      <c r="B45" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>1241</v>
-      </c>
-      <c r="G45" t="s">
-        <v>1</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>1242</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>1243</v>
-      </c>
-      <c r="B46" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>1244</v>
-      </c>
-      <c r="G46" t="s">
-        <v>1</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>1242</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>1245</v>
-      </c>
-      <c r="B47" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>1133</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G47" t="s">
-        <v>1</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>1246</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>1247</v>
-      </c>
-      <c r="B48" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>1248</v>
-      </c>
-      <c r="G48" t="s">
-        <v>1</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>1249</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>1250</v>
-      </c>
-      <c r="B49" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>1251</v>
-      </c>
-      <c r="G49" t="s">
-        <v>1</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>1252</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>1253</v>
-      </c>
-      <c r="B50" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>1254</v>
-      </c>
-      <c r="G50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>1252</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>1255</v>
-      </c>
-      <c r="B51" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>1256</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G51" t="s">
-        <v>1</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>1257</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>1258</v>
-      </c>
-      <c r="B52" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>1259</v>
-      </c>
-      <c r="G52" t="s">
-        <v>1</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>1261</v>
-      </c>
-      <c r="B53" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>1262</v>
-      </c>
-      <c r="G53" t="s">
-        <v>1</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>1263</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>1264</v>
-      </c>
-      <c r="B54" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>1265</v>
-      </c>
-      <c r="G54" t="s">
-        <v>1</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>1263</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>1266</v>
-      </c>
-      <c r="B55" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>1267</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G55" t="s">
-        <v>1</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>1268</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>1269</v>
-      </c>
-      <c r="B56" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E56" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>1270</v>
-      </c>
-      <c r="G56" t="s">
-        <v>1</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>1271</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>1272</v>
-      </c>
-      <c r="B57" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E57" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>1273</v>
-      </c>
-      <c r="G57" t="s">
-        <v>1</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>1271</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>1274</v>
-      </c>
-      <c r="B58" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>1275</v>
-      </c>
-      <c r="G58" t="s">
-        <v>1</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>1276</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>1277</v>
-      </c>
-      <c r="B59" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>1278</v>
-      </c>
-      <c r="G59" t="s">
-        <v>1</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>1276</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>1279</v>
-      </c>
-      <c r="B60" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>1280</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G60" t="s">
-        <v>1</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>1281</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>1282</v>
-      </c>
-      <c r="B61" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>1283</v>
-      </c>
-      <c r="G61" t="s">
-        <v>1</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>1284</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>1285</v>
-      </c>
-      <c r="B62" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>1286</v>
-      </c>
-      <c r="G62" t="s">
-        <v>1</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>1284</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>1287</v>
-      </c>
-      <c r="B63" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E63" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>1288</v>
-      </c>
-      <c r="G63" t="s">
-        <v>1</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>1289</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>1290</v>
-      </c>
-      <c r="B64" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E64" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>1291</v>
-      </c>
-      <c r="G64" t="s">
-        <v>1</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>1289</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>1292</v>
-      </c>
-      <c r="B65" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>1293</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G65" t="s">
-        <v>1</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>1294</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>1295</v>
-      </c>
-      <c r="B66" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>1296</v>
-      </c>
-      <c r="G66" t="s">
-        <v>1</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>1297</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>1298</v>
-      </c>
-      <c r="B67" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E67" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>1299</v>
-      </c>
-      <c r="G67" t="s">
-        <v>1</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>1297</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>1300</v>
-      </c>
-      <c r="B68" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>1301</v>
-      </c>
-      <c r="G68" t="s">
-        <v>1</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>1302</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>1303</v>
-      </c>
-      <c r="B69" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E69" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>1304</v>
-      </c>
-      <c r="G69" t="s">
-        <v>1</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>1302</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>1305</v>
-      </c>
-      <c r="B70" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>1306</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G70" t="s">
-        <v>1</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>1307</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>1308</v>
-      </c>
-      <c r="B71" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>1309</v>
-      </c>
-      <c r="G71" t="s">
-        <v>1</v>
-      </c>
-      <c r="H71" s="3" t="s">
-        <v>1310</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>1311</v>
-      </c>
-      <c r="B72" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E72" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>1312</v>
-      </c>
-      <c r="G72" t="s">
-        <v>1</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>1310</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>1313</v>
-      </c>
-      <c r="B73" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E73" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>1314</v>
-      </c>
-      <c r="G73" t="s">
-        <v>1</v>
-      </c>
-      <c r="H73" s="3" t="s">
-        <v>1315</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>1316</v>
-      </c>
-      <c r="B74" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>1317</v>
-      </c>
-      <c r="G74" t="s">
-        <v>1</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>1315</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B75" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C75" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>1319</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G75" t="s">
-        <v>1</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>1321</v>
-      </c>
-      <c r="B76" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E76" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>1322</v>
-      </c>
-      <c r="G76" t="s">
-        <v>1</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>1323</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>1324</v>
-      </c>
-      <c r="B77" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>1325</v>
-      </c>
-      <c r="G77" t="s">
-        <v>1</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>1323</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>1326</v>
-      </c>
-      <c r="B78" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>1327</v>
-      </c>
-      <c r="G78" t="s">
-        <v>1</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>1323</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>1328</v>
-      </c>
-      <c r="B79" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F79" s="3" t="s">
-        <v>1329</v>
-      </c>
-      <c r="G79" t="s">
-        <v>1</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>1330</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>1331</v>
-      </c>
-      <c r="B80" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>1332</v>
-      </c>
-      <c r="G80" t="s">
-        <v>1</v>
-      </c>
-      <c r="H80" s="3" t="s">
-        <v>1330</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>1333</v>
-      </c>
-      <c r="B81" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>1334</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G81" t="s">
-        <v>1</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>1335</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>1336</v>
-      </c>
-      <c r="B82" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E82" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>1337</v>
-      </c>
-      <c r="G82" t="s">
-        <v>1</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>1338</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>1339</v>
-      </c>
-      <c r="B83" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E83" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>1340</v>
-      </c>
-      <c r="G83" t="s">
-        <v>1</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>1342</v>
-      </c>
-      <c r="B84" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E84" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>1343</v>
-      </c>
-      <c r="G84" t="s">
-        <v>1</v>
-      </c>
-      <c r="H84" s="3" t="s">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>1344</v>
-      </c>
-      <c r="B85" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C85" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>1345</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G85" t="s">
-        <v>1</v>
-      </c>
-      <c r="H85" s="3" t="s">
-        <v>1346</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>1347</v>
-      </c>
-      <c r="B86" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>1348</v>
-      </c>
-      <c r="G86" t="s">
-        <v>1</v>
-      </c>
-      <c r="H86" s="3" t="s">
-        <v>1349</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>1350</v>
-      </c>
-      <c r="B87" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E87" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>1351</v>
-      </c>
-      <c r="G87" t="s">
-        <v>1</v>
-      </c>
-      <c r="H87" s="3" t="s">
-        <v>1352</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>1353</v>
-      </c>
-      <c r="B88" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F88" s="3" t="s">
-        <v>1354</v>
-      </c>
-      <c r="G88" t="s">
-        <v>1</v>
-      </c>
-      <c r="H88" s="3" t="s">
-        <v>1352</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>1355</v>
-      </c>
-      <c r="B89" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>1356</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G89" t="s">
-        <v>1</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>1357</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>1358</v>
-      </c>
-      <c r="B90" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E90" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>1359</v>
-      </c>
-      <c r="G90" t="s">
-        <v>1</v>
-      </c>
-      <c r="H90" s="3" t="s">
-        <v>1360</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>1361</v>
-      </c>
-      <c r="B91" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>1362</v>
-      </c>
-      <c r="G91" t="s">
-        <v>1</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>1360</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>1363</v>
-      </c>
-      <c r="B92" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E92" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F92" s="3" t="s">
-        <v>1364</v>
-      </c>
-      <c r="G92" t="s">
-        <v>1</v>
-      </c>
-      <c r="H92" s="3" t="s">
-        <v>1365</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>1366</v>
-      </c>
-      <c r="B93" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E93" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F93" s="3" t="s">
-        <v>1367</v>
-      </c>
-      <c r="G93" t="s">
-        <v>1</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>1365</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>1368</v>
-      </c>
-      <c r="B94" t="s">
-        <v>1369</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E94" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>1370</v>
-      </c>
-      <c r="G94" t="s">
-        <v>1</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>1371</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>1372</v>
-      </c>
-      <c r="B95" t="s">
-        <v>1369</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E95" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F95" s="3" t="s">
-        <v>1373</v>
-      </c>
-      <c r="G95" t="s">
-        <v>1</v>
-      </c>
-      <c r="H95" s="3" t="s">
-        <v>1374</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>1375</v>
-      </c>
-      <c r="B96" t="s">
-        <v>1369</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E96" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>1376</v>
-      </c>
-      <c r="G96" t="s">
-        <v>1</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>1377</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>1378</v>
-      </c>
-      <c r="B97" t="s">
-        <v>1369</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E97" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F97" s="3" t="s">
-        <v>1379</v>
-      </c>
-      <c r="G97" t="s">
-        <v>1</v>
-      </c>
-      <c r="H97" s="3" t="s">
-        <v>1377</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>1380</v>
-      </c>
-      <c r="B98" t="s">
-        <v>1369</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E98" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F98" s="3" t="s">
-        <v>1381</v>
-      </c>
-      <c r="G98" t="s">
-        <v>1</v>
-      </c>
-      <c r="H98" s="3" t="s">
-        <v>1377</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>1382</v>
-      </c>
-      <c r="B99" t="s">
-        <v>1369</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E99" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F99" s="3" t="s">
-        <v>1383</v>
-      </c>
-      <c r="G99" t="s">
-        <v>1</v>
-      </c>
-      <c r="H99" s="3" t="s">
-        <v>1377</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>1384</v>
-      </c>
-      <c r="B100" t="s">
-        <v>1369</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E100" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>1385</v>
-      </c>
-      <c r="G100" t="s">
-        <v>1</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>1377</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>1386</v>
-      </c>
-      <c r="B101" t="s">
-        <v>1369</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E101" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>1387</v>
-      </c>
-      <c r="G101" t="s">
-        <v>1</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>1377</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>1388</v>
-      </c>
-      <c r="B102" t="s">
-        <v>1369</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E102" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>1389</v>
-      </c>
-      <c r="G102" t="s">
-        <v>1</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>1377</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>1390</v>
-      </c>
-      <c r="B103" t="s">
-        <v>1369</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E103" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F103" s="3" t="s">
-        <v>1391</v>
-      </c>
-      <c r="G103" t="s">
-        <v>1</v>
-      </c>
-      <c r="H103" s="3" t="s">
-        <v>1377</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>1392</v>
-      </c>
-      <c r="B104" t="s">
-        <v>1369</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D104" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E104" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F104" s="3" t="s">
-        <v>1393</v>
-      </c>
-      <c r="G104" t="s">
-        <v>1</v>
-      </c>
-      <c r="H104" s="3" t="s">
-        <v>1394</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>1395</v>
-      </c>
-      <c r="B105" t="s">
-        <v>1369</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D105" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E105" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F105" s="3" t="s">
-        <v>1396</v>
-      </c>
-      <c r="G105" t="s">
-        <v>1</v>
-      </c>
-      <c r="H105" s="3" t="s">
-        <v>1397</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>1398</v>
-      </c>
-      <c r="B106" t="s">
-        <v>1369</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D106" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E106" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F106" s="3" t="s">
-        <v>1399</v>
-      </c>
-      <c r="G106" t="s">
-        <v>1</v>
-      </c>
-      <c r="H106" s="3" t="s">
-        <v>1397</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>1400</v>
-      </c>
-      <c r="B107" t="s">
-        <v>1369</v>
-      </c>
-      <c r="C107" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D107" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E107" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F107" s="3" t="s">
-        <v>1401</v>
-      </c>
-      <c r="G107" t="s">
-        <v>1</v>
-      </c>
-      <c r="H107" s="3" t="s">
-        <v>1397</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>1402</v>
-      </c>
-      <c r="B108" t="s">
-        <v>1369</v>
-      </c>
-      <c r="C108" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D108" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E108" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F108" s="3" t="s">
-        <v>1403</v>
-      </c>
-      <c r="G108" t="s">
-        <v>1</v>
-      </c>
-      <c r="H108" s="3" t="s">
-        <v>1397</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>1404</v>
-      </c>
-      <c r="B109" t="s">
-        <v>1369</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D109" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E109" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F109" s="3" t="s">
-        <v>1405</v>
-      </c>
-      <c r="G109" t="s">
-        <v>1</v>
-      </c>
-      <c r="H109" s="3" t="s">
-        <v>1397</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>1406</v>
-      </c>
-      <c r="B110" t="s">
-        <v>1369</v>
-      </c>
-      <c r="C110" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D110" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E110" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F110" s="3" t="s">
-        <v>1407</v>
-      </c>
-      <c r="G110" t="s">
-        <v>1</v>
-      </c>
-      <c r="H110" s="3" t="s">
-        <v>1397</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>1408</v>
-      </c>
-      <c r="B111" t="s">
-        <v>1369</v>
-      </c>
-      <c r="C111" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D111" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E111" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F111" s="3" t="s">
-        <v>1409</v>
-      </c>
-      <c r="G111" t="s">
-        <v>1</v>
-      </c>
-      <c r="H111" s="3" t="s">
-        <v>1397</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>1410</v>
-      </c>
-      <c r="B112" t="s">
-        <v>1369</v>
-      </c>
-      <c r="C112" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D112" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E112" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F112" s="3" t="s">
-        <v>1411</v>
-      </c>
-      <c r="G112" t="s">
-        <v>1</v>
-      </c>
-      <c r="H112" s="3" t="s">
-        <v>1412</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>1413</v>
-      </c>
-      <c r="B113" t="s">
-        <v>1369</v>
-      </c>
-      <c r="C113" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D113" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E113" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F113" s="3" t="s">
-        <v>1414</v>
-      </c>
-      <c r="G113" t="s">
-        <v>1</v>
-      </c>
-      <c r="H113" s="3" t="s">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>1416</v>
-      </c>
-      <c r="B114" t="s">
-        <v>1369</v>
-      </c>
-      <c r="C114" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D114" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E114" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F114" s="3" t="s">
-        <v>1417</v>
-      </c>
-      <c r="G114" t="s">
-        <v>1</v>
-      </c>
-      <c r="H114" s="3" t="s">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>1418</v>
-      </c>
-      <c r="B115" t="s">
-        <v>1369</v>
-      </c>
-      <c r="C115" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D115" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E115" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F115" s="3" t="s">
-        <v>1419</v>
-      </c>
-      <c r="G115" t="s">
-        <v>1</v>
-      </c>
-      <c r="H115" s="3" t="s">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>1420</v>
-      </c>
-      <c r="B116" t="s">
-        <v>1369</v>
-      </c>
-      <c r="C116" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D116" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E116" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F116" s="3" t="s">
-        <v>1421</v>
-      </c>
-      <c r="G116" t="s">
-        <v>1</v>
-      </c>
-      <c r="H116" s="3" t="s">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>1422</v>
-      </c>
-      <c r="B117" t="s">
-        <v>1369</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D117" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E117" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F117" s="3" t="s">
-        <v>1423</v>
-      </c>
-      <c r="G117" t="s">
-        <v>1</v>
-      </c>
-      <c r="H117" s="3" t="s">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>1424</v>
-      </c>
-      <c r="B118" t="s">
-        <v>1369</v>
-      </c>
-      <c r="C118" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D118" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E118" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F118" s="3" t="s">
-        <v>1425</v>
-      </c>
-      <c r="G118" t="s">
-        <v>1</v>
-      </c>
-      <c r="H118" s="3" t="s">
-        <v>1415</v>
       </c>
     </row>
   </sheetData>
